--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B2896EA-943A-4090-802B-E001F5288BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8380A2-5DA5-4BBE-8065-5B380C0E6FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
+    <workbookView xWindow="1980" yWindow="1980" windowWidth="21600" windowHeight="11295" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
   <sheets>
     <sheet name="TransaccionesSAP" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>Transaction</t>
   </si>
@@ -34,24 +34,15 @@
     <t>Step3</t>
   </si>
   <si>
-    <t>ZMG002_01</t>
-  </si>
-  <si>
     <t>variante</t>
   </si>
   <si>
     <t>ejecutar</t>
   </si>
   <si>
-    <t>ZMM026</t>
-  </si>
-  <si>
     <t>disposicion</t>
   </si>
   <si>
-    <t>LX02</t>
-  </si>
-  <si>
     <t>COHV</t>
   </si>
   <si>
@@ -89,13 +80,16 @@
   </si>
   <si>
     <t>ODM</t>
+  </si>
+  <si>
+    <t>Step4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +220,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -572,8 +572,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -633,9 +634,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -673,7 +674,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -779,7 +780,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -921,7 +922,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -929,10 +930,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -945,111 +946,103 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
         <v>5</v>
       </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
         <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8380A2-5DA5-4BBE-8065-5B380C0E6FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C5B2F4-912A-4821-BFBD-F55B2CC3C1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1980" windowWidth="21600" windowHeight="11295" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
   <sheets>
     <sheet name="TransaccionesSAP" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>Transaction</t>
   </si>
@@ -41,15 +41,6 @@
   </si>
   <si>
     <t>disposicion</t>
-  </si>
-  <si>
-    <t>COHV</t>
-  </si>
-  <si>
-    <t>checks</t>
-  </si>
-  <si>
-    <t>ZCO017</t>
   </si>
   <si>
     <t>ZPP029_1</t>
@@ -572,9 +563,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -930,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -947,21 +937,15 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -982,6 +966,12 @@
       <c r="B4" t="s">
         <v>11</v>
       </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1002,43 +992,18 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>6</v>
+      <c r="E6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
       <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
         <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C5B2F4-912A-4821-BFBD-F55B2CC3C1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6980C48E-D965-44A3-9FDE-15CDAA6DB959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Transaction</t>
   </si>
@@ -43,37 +43,28 @@
     <t>disposicion</t>
   </si>
   <si>
-    <t>ZPP029_1</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>MB52</t>
-  </si>
-  <si>
     <t>ZSD053</t>
   </si>
   <si>
+    <t>LT23</t>
+  </si>
+  <si>
+    <t>VL06O</t>
+  </si>
+  <si>
+    <t>listas sal</t>
+  </si>
+  <si>
+    <t>vista posicion</t>
+  </si>
+  <si>
+    <t>ODM</t>
+  </si>
+  <si>
+    <t>Step4</t>
+  </si>
+  <si>
     <t>filtrar pedido</t>
-  </si>
-  <si>
-    <t>LT23</t>
-  </si>
-  <si>
-    <t>VL06O</t>
-  </si>
-  <si>
-    <t>listas sal</t>
-  </si>
-  <si>
-    <t>vista posicion</t>
-  </si>
-  <si>
-    <t>ODM</t>
-  </si>
-  <si>
-    <t>Step4</t>
   </si>
 </sst>
 </file>
@@ -920,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -937,7 +928,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -945,12 +936,18 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -961,49 +958,24 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6980C48E-D965-44A3-9FDE-15CDAA6DB959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9210DF9-1900-4543-A17D-13EC8041A311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Transaction</t>
   </si>
@@ -34,37 +34,10 @@
     <t>Step3</t>
   </si>
   <si>
-    <t>variante</t>
-  </si>
-  <si>
-    <t>ejecutar</t>
-  </si>
-  <si>
-    <t>disposicion</t>
-  </si>
-  <si>
-    <t>ZSD053</t>
-  </si>
-  <si>
-    <t>LT23</t>
-  </si>
-  <si>
-    <t>VL06O</t>
-  </si>
-  <si>
-    <t>listas sal</t>
-  </si>
-  <si>
-    <t>vista posicion</t>
-  </si>
-  <si>
     <t>ODM</t>
   </si>
   <si>
     <t>Step4</t>
-  </si>
-  <si>
-    <t>filtrar pedido</t>
   </si>
 </sst>
 </file>
@@ -911,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -928,54 +901,12 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
       <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9210DF9-1900-4543-A17D-13EC8041A311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5A05C-60BD-4EC1-A074-DCA3DDA413D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Transaction</t>
   </si>
@@ -34,10 +34,64 @@
     <t>Step3</t>
   </si>
   <si>
+    <t>ZMG002_01</t>
+  </si>
+  <si>
+    <t>variante</t>
+  </si>
+  <si>
+    <t>ejecutar</t>
+  </si>
+  <si>
+    <t>ZMM026</t>
+  </si>
+  <si>
+    <t>disposicion</t>
+  </si>
+  <si>
+    <t>LX02</t>
+  </si>
+  <si>
+    <t>COHV</t>
+  </si>
+  <si>
+    <t>checks</t>
+  </si>
+  <si>
+    <t>ZCO017</t>
+  </si>
+  <si>
+    <t>ZPP029_1</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>MB52</t>
+  </si>
+  <si>
+    <t>ZSD053</t>
+  </si>
+  <si>
+    <t>LT23</t>
+  </si>
+  <si>
+    <t>VL06O</t>
+  </si>
+  <si>
+    <t>listas sal</t>
+  </si>
+  <si>
+    <t>vista posicion</t>
+  </si>
+  <si>
     <t>ODM</t>
   </si>
   <si>
     <t>Step4</t>
+  </si>
+  <si>
+    <t>filtrar pedido</t>
   </si>
 </sst>
 </file>
@@ -884,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -901,12 +955,131 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5A05C-60BD-4EC1-A074-DCA3DDA413D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1E70CE-48A8-4AA8-BCF3-57A0E313AB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>Transaction</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Step3</t>
-  </si>
-  <si>
-    <t>ZMG002_01</t>
   </si>
   <si>
     <t>variante</t>
@@ -938,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,29 +952,29 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -985,24 +982,24 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1010,18 +1007,18 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1029,10 +1026,13 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="C8" t="s">
-        <v>6</v>
+      <c r="D8" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1040,13 +1040,10 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1054,32 +1051,21 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
         <v>5</v>
       </c>
-      <c r="C10" t="s">
-        <v>6</v>
+      <c r="E10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
       <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1E70CE-48A8-4AA8-BCF3-57A0E313AB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5A05C-60BD-4EC1-A074-DCA3DDA413D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Transaction</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>Step3</t>
+  </si>
+  <si>
+    <t>ZMG002_01</t>
   </si>
   <si>
     <t>variante</t>
@@ -935,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -952,29 +955,29 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -982,24 +985,24 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1007,18 +1010,18 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,13 +1029,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1040,10 +1040,13 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1051,21 +1054,32 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
         <v>5</v>
       </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5A05C-60BD-4EC1-A074-DCA3DDA413D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87B7E26-03D8-4547-B2AE-0FC72D09FC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Transaction</t>
   </si>
@@ -34,31 +34,13 @@
     <t>Step3</t>
   </si>
   <si>
-    <t>ZMG002_01</t>
-  </si>
-  <si>
     <t>variante</t>
   </si>
   <si>
     <t>ejecutar</t>
   </si>
   <si>
-    <t>ZMM026</t>
-  </si>
-  <si>
-    <t>disposicion</t>
-  </si>
-  <si>
     <t>LX02</t>
-  </si>
-  <si>
-    <t>COHV</t>
-  </si>
-  <si>
-    <t>checks</t>
-  </si>
-  <si>
-    <t>ZCO017</t>
   </si>
   <si>
     <t>ZPP029_1</t>
@@ -67,31 +49,7 @@
     <t>BOM</t>
   </si>
   <si>
-    <t>MB52</t>
-  </si>
-  <si>
-    <t>ZSD053</t>
-  </si>
-  <si>
-    <t>LT23</t>
-  </si>
-  <si>
-    <t>VL06O</t>
-  </si>
-  <si>
-    <t>listas sal</t>
-  </si>
-  <si>
-    <t>vista posicion</t>
-  </si>
-  <si>
-    <t>ODM</t>
-  </si>
-  <si>
     <t>Step4</t>
-  </si>
-  <si>
-    <t>filtrar pedido</t>
   </si>
 </sst>
 </file>
@@ -581,8 +539,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -938,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,131 +914,26 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP06_00_InformeSeguimientoRepuestos\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87B7E26-03D8-4547-B2AE-0FC72D09FC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5A05C-60BD-4EC1-A074-DCA3DDA413D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Transaction</t>
   </si>
@@ -34,22 +34,64 @@
     <t>Step3</t>
   </si>
   <si>
+    <t>ZMG002_01</t>
+  </si>
+  <si>
     <t>variante</t>
   </si>
   <si>
     <t>ejecutar</t>
   </si>
   <si>
+    <t>ZMM026</t>
+  </si>
+  <si>
+    <t>disposicion</t>
+  </si>
+  <si>
     <t>LX02</t>
   </si>
   <si>
+    <t>COHV</t>
+  </si>
+  <si>
+    <t>checks</t>
+  </si>
+  <si>
+    <t>ZCO017</t>
+  </si>
+  <si>
     <t>ZPP029_1</t>
   </si>
   <si>
     <t>BOM</t>
   </si>
   <si>
+    <t>MB52</t>
+  </si>
+  <si>
+    <t>ZSD053</t>
+  </si>
+  <si>
+    <t>LT23</t>
+  </si>
+  <si>
+    <t>VL06O</t>
+  </si>
+  <si>
+    <t>listas sal</t>
+  </si>
+  <si>
+    <t>vista posicion</t>
+  </si>
+  <si>
+    <t>ODM</t>
+  </si>
+  <si>
     <t>Step4</t>
+  </si>
+  <si>
+    <t>filtrar pedido</t>
   </si>
 </sst>
 </file>
@@ -539,9 +581,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -897,7 +938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -914,26 +955,131 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
